--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Исламова- делопроизводитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Исламова- делопроизводитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92575370552</v>
+        <v>46157.93119666893</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Исламова- делопроизводитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Исламова- делопроизводитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93119666893</v>
+        <v>46157.93185536828</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Исламова- делопроизводитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Исламова- делопроизводитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93185536828</v>
+        <v>46157.93406748644</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Исламова- делопроизводитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Исламова- делопроизводитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93406748644</v>
+        <v>46157.93724839625</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Исламова- делопроизводитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Исламова- делопроизводитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93724839625</v>
+        <v>46158.28222466462</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Исламова- делопроизводитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Исламова- делопроизводитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28222466462</v>
+        <v>46158.29708830604</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Исламова- делопроизводитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Исламова- делопроизводитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29708830604</v>
+        <v>46158.29822401414</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Исламова- делопроизводитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Исламова- делопроизводитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29822401414</v>
+        <v>46158.33393408269</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Исламова- делопроизводитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Исламова- делопроизводитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33393408269</v>
+        <v>46158.36863194536</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Исламова- делопроизводитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Исламова- делопроизводитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36863194536</v>
+        <v>46158.3729415999</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
